--- a/49845_Intercuenca_Medio_Huallaga/_raw_reportes_xlsx/IDConfig_65112_completo.xlsx
+++ b/49845_Intercuenca_Medio_Huallaga/_raw_reportes_xlsx/IDConfig_65112_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R0130d19484c944ab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Ra8f784c38a0843ab"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,486 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.5400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.5500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.5600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.5100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.5200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.5400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.5300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.5400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.6300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.6600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.6700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.6800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.7200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.7600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.7000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.6400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.5700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.5800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.6300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.6700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.5200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.5500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.5800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.5500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.3900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.3900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.3900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.4000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.4200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.4200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.4300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.4300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>15/08/2026</x:t>
         </x:is>
       </x:c>

--- a/49845_Intercuenca_Medio_Huallaga/_raw_reportes_xlsx/IDConfig_65112_completo.xlsx
+++ b/49845_Intercuenca_Medio_Huallaga/_raw_reportes_xlsx/IDConfig_65112_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Ra8f784c38a0843ab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R4c828cd41dd64254"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,2856 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>11/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.6400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.6900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.7400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     15.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     15.3500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.6000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.4200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.4400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.4200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.3900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.3600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.3700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.3700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.3800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.3800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.4000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.4100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.4300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.4600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.4800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.5000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.5200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.5400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.6000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.6500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.6500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.6600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.7300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.7600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.7900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.8100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.9800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     15.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     15.0500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     15.0200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.8000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.8400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.8600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.8400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.4500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.4700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.4900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.5100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.7000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.7200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.7400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.7600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.8000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.8200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.8500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.8600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.8100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.7500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.6100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.5000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.5300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.5400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.5400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.5600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.5900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.5700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.6100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.6500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.6200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.6000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.5900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.6000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.6500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.6800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.7000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.6500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.5100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.5400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.5500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.5700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.6400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.6700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.7100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.7500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.8400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.9000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.9300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.9600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     15.2900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     15.3400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     15.2300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     15.1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.8300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.8100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.8000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.8200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.8200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.8400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.9000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.9400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.8000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.8400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.8600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.8800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     15.2200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     15.2700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     15.4000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     15.5000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     15.1500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.4200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.3900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.3700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.3500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.3500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.3600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.3600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.3700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.3800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.3900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.4000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.4200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.4400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.4600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.4700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.4800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.5100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.5700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.6200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.5000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.5200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.5500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.5200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.4200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.4400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.4600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.4800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.2800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.2700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.2700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.2800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.2900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.2900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.3000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.3000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.3200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.3200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.3300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.3400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.3500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.3500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.3600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.3600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.3700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.3800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.3900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.4000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.3200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.3300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.3500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.3800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.4100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.4100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.4200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.4200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.3900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.4000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.4100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.4200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.4600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.4800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.5100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.5300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.5200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.5600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.6200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.6600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.6900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.7200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.7600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.8000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.9800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     15.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     15.0500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     15.0800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     15.3800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     15.3500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     15.2200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     15.1500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.9500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.9000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.7900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.7200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.7500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.6700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.5900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>24/08/2026</x:t>
         </x:is>
       </x:c>
